--- a/p6_deployment/data/italy/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/p6_deployment/data/italy/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C906"/>
+  <dimension ref="A1:C1014"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14028,6 +14028,1317 @@
         <v>183</v>
       </c>
     </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr"/>
+      <c r="C907" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dionisi f 
+  ita </t>
+        </is>
+      </c>
+      <c r="C908" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sozza s 
+  ita </t>
+        </is>
+      </c>
+      <c r="C909" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t xml:space="preserve">caputi m 
+  ita </t>
+        </is>
+      </c>
+      <c r="C910" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orsato d 
+  ita </t>
+        </is>
+      </c>
+      <c r="C911" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr"/>
+      <c r="C912" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr"/>
+      <c r="C913" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr"/>
+      <c r="C914" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr"/>
+      <c r="C915" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr"/>
+      <c r="C916" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr"/>
+      <c r="C917" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr"/>
+      <c r="C918" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr"/>
+      <c r="C919" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr"/>
+      <c r="C920" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr"/>
+      <c r="C921" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr"/>
+      <c r="C922" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr"/>
+      <c r="C923" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr"/>
+      <c r="C924" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr"/>
+      <c r="C925" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr"/>
+      <c r="C926" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr"/>
+      <c r="C927" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unipol domus
+  cagliari </t>
+        </is>
+      </c>
+      <c r="C928" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio renato dall ara
+  bologna </t>
+        </is>
+      </c>
+      <c r="C929" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
+        </is>
+      </c>
+      <c r="C930" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
+        </is>
+      </c>
+      <c r="C931" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio ennio tardini
+  parma </t>
+        </is>
+      </c>
+      <c r="C932" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio arechi
+  salerno </t>
+        </is>
+      </c>
+      <c r="C933" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico di torino
+  turin </t>
+        </is>
+      </c>
+      <c r="C934" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
+        </is>
+      </c>
+      <c r="C935" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio ennio tardini
+  parma </t>
+        </is>
+      </c>
+      <c r="C936" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio mario rigamonti
+  brescia </t>
+        </is>
+      </c>
+      <c r="C937" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio diego armando maradona
+  naples </t>
+        </is>
+      </c>
+      <c r="C938" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giovanni zini
+  cremona </t>
+        </is>
+      </c>
+      <c r="C939" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brianteo
+  monza </t>
+        </is>
+      </c>
+      <c r="C940" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
+        </is>
+      </c>
+      <c r="C941" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapei stadium – citta del tricolore
+  reggio emilia </t>
+        </is>
+      </c>
+      <c r="C942" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio dino manuzzi
+  cesena </t>
+        </is>
+      </c>
+      <c r="C943" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio romeo menti
+  castellammare di stabia </t>
+        </is>
+      </c>
+      <c r="C944" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vanni sanna
+  sassari </t>
+        </is>
+      </c>
+      <c r="C945" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio dei marmi
+  carrara </t>
+        </is>
+      </c>
+      <c r="C946" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>id_team_home</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>UiGfvfvT</t>
+        </is>
+      </c>
+      <c r="C947" t="n">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr"/>
+      <c r="C948" t="n">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr"/>
+      <c r="C949" t="n">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr"/>
+      <c r="C950" t="n">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr"/>
+      <c r="C951" t="n">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr"/>
+      <c r="C952" t="n">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>tYVGfTo2</t>
+        </is>
+      </c>
+      <c r="C953" t="n">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr"/>
+      <c r="C954" t="n">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr"/>
+      <c r="C955" t="n">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr"/>
+      <c r="C956" t="n">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr"/>
+      <c r="C957" t="n">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr"/>
+      <c r="C958" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr"/>
+      <c r="C959" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr"/>
+      <c r="C960" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr"/>
+      <c r="C961" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr"/>
+      <c r="C962" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr"/>
+      <c r="C963" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr"/>
+      <c r="C964" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr"/>
+      <c r="C965" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr"/>
+      <c r="C966" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr"/>
+      <c r="C967" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr"/>
+      <c r="C968" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr"/>
+      <c r="C969" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr"/>
+      <c r="C970" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr"/>
+      <c r="C971" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr"/>
+      <c r="C972" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr"/>
+      <c r="C973" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr"/>
+      <c r="C974" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr"/>
+      <c r="C975" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr"/>
+      <c r="C976" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr"/>
+      <c r="C977" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr"/>
+      <c r="C978" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr"/>
+      <c r="C979" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr"/>
+      <c r="C980" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr"/>
+      <c r="C981" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr"/>
+      <c r="C982" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr"/>
+      <c r="C983" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr"/>
+      <c r="C984" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr"/>
+      <c r="C985" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr"/>
+      <c r="C986" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr"/>
+      <c r="C987" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr"/>
+      <c r="C988" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr"/>
+      <c r="C989" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr"/>
+      <c r="C990" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr"/>
+      <c r="C991" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr"/>
+      <c r="C992" t="n">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr"/>
+      <c r="C993" t="n">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr"/>
+      <c r="C994" t="n">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr"/>
+      <c r="C995" t="n">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr"/>
+      <c r="C996" t="n">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr"/>
+      <c r="C997" t="n">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr"/>
+      <c r="C998" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr"/>
+      <c r="C999" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr"/>
+      <c r="C1000" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr"/>
+      <c r="C1001" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr"/>
+      <c r="C1002" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr"/>
+      <c r="C1003" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr"/>
+      <c r="C1004" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr"/>
+      <c r="C1005" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr"/>
+      <c r="C1006" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr"/>
+      <c r="C1007" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr"/>
+      <c r="C1008" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr"/>
+      <c r="C1009" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr"/>
+      <c r="C1010" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr"/>
+      <c r="C1011" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr"/>
+      <c r="C1012" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr"/>
+      <c r="C1013" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr"/>
+      <c r="C1014" t="n">
+        <v>185</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/italy/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/p6_deployment/data/italy/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1014"/>
+  <dimension ref="A1:C1092"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15339,6 +15339,894 @@
         <v>185</v>
       </c>
     </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr"/>
+      <c r="C1015" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr"/>
+      <c r="C1016" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr"/>
+      <c r="C1017" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr"/>
+      <c r="C1018" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr"/>
+      <c r="C1019" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr"/>
+      <c r="C1020" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr"/>
+      <c r="C1021" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr"/>
+      <c r="C1022" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr"/>
+      <c r="C1023" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr"/>
+      <c r="C1024" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr"/>
+      <c r="C1025" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr"/>
+      <c r="C1026" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr"/>
+      <c r="C1027" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr"/>
+      <c r="C1028" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr"/>
+      <c r="C1029" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr"/>
+      <c r="C1030" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr"/>
+      <c r="C1031" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr"/>
+      <c r="C1032" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr"/>
+      <c r="C1033" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr"/>
+      <c r="C1034" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr"/>
+      <c r="C1035" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr"/>
+      <c r="C1036" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr"/>
+      <c r="C1037" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr"/>
+      <c r="C1038" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr"/>
+      <c r="C1039" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr"/>
+      <c r="C1040" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr"/>
+      <c r="C1041" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz stadium
+  turin </t>
+        </is>
+      </c>
+      <c r="C1042" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio via del mare
+  lecce </t>
+        </is>
+      </c>
+      <c r="C1043" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio san vito luigi marulla
+  cosenza </t>
+        </is>
+      </c>
+      <c r="C1044" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr"/>
+      <c r="C1045" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arena garibaldi   stadio romeo anconetani
+  pisa </t>
+        </is>
+      </c>
+      <c r="C1046" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio san nicola
+  bari </t>
+        </is>
+      </c>
+      <c r="C1047" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio marco druso
+  bolzano </t>
+        </is>
+      </c>
+      <c r="C1048" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr"/>
+      <c r="C1049" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr"/>
+      <c r="C1050" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr"/>
+      <c r="C1051" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr"/>
+      <c r="C1052" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr"/>
+      <c r="C1053" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr"/>
+      <c r="C1054" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr"/>
+      <c r="C1055" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr"/>
+      <c r="C1056" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr"/>
+      <c r="C1057" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr"/>
+      <c r="C1058" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr"/>
+      <c r="C1059" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr"/>
+      <c r="C1060" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr"/>
+      <c r="C1061" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1062" t="inlineStr"/>
+      <c r="C1062" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr"/>
+      <c r="C1063" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1064" t="inlineStr"/>
+      <c r="C1064" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr"/>
+      <c r="C1065" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr"/>
+      <c r="C1066" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr"/>
+      <c r="C1067" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr"/>
+      <c r="C1068" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr"/>
+      <c r="C1069" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr"/>
+      <c r="C1070" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr"/>
+      <c r="C1071" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr"/>
+      <c r="C1072" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr"/>
+      <c r="C1073" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr"/>
+      <c r="C1074" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr"/>
+      <c r="C1075" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr"/>
+      <c r="C1076" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr"/>
+      <c r="C1077" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr"/>
+      <c r="C1078" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr"/>
+      <c r="C1079" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr"/>
+      <c r="C1080" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr"/>
+      <c r="C1081" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr"/>
+      <c r="C1082" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr"/>
+      <c r="C1083" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr"/>
+      <c r="C1084" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr"/>
+      <c r="C1085" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr"/>
+      <c r="C1086" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr"/>
+      <c r="C1087" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr"/>
+      <c r="C1088" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr"/>
+      <c r="C1089" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr"/>
+      <c r="C1090" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr"/>
+      <c r="C1091" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr"/>
+      <c r="C1092" t="n">
+        <v>186</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/italy/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/p6_deployment/data/italy/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1089"/>
+  <dimension ref="A1:C1109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16919,6 +16919,226 @@
         <v>255</v>
       </c>
     </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr"/>
+      <c r="C1090" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr"/>
+      <c r="C1091" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr"/>
+      <c r="C1092" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr"/>
+      <c r="C1093" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr"/>
+      <c r="C1094" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr"/>
+      <c r="C1095" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr"/>
+      <c r="C1096" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr"/>
+      <c r="C1097" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr"/>
+      <c r="C1098" t="n">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr"/>
+      <c r="C1099" t="n">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr"/>
+      <c r="C1100" t="n">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr"/>
+      <c r="C1101" t="n">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr"/>
+      <c r="C1102" t="n">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr"/>
+      <c r="C1103" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr"/>
+      <c r="C1104" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr"/>
+      <c r="C1105" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr"/>
+      <c r="C1106" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr"/>
+      <c r="C1107" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr"/>
+      <c r="C1108" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr"/>
+      <c r="C1109" t="n">
+        <v>256</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/italy/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/p6_deployment/data/italy/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1109"/>
+  <dimension ref="A1:C1167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17139,6 +17139,644 @@
         <v>256</v>
       </c>
     </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr"/>
+      <c r="C1110" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr"/>
+      <c r="C1111" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr"/>
+      <c r="C1112" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr"/>
+      <c r="C1113" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr"/>
+      <c r="C1114" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr"/>
+      <c r="C1115" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr"/>
+      <c r="C1116" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr"/>
+      <c r="C1117" t="n">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr"/>
+      <c r="C1118" t="n">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr"/>
+      <c r="C1119" t="n">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr"/>
+      <c r="C1120" t="n">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr"/>
+      <c r="C1121" t="n">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr"/>
+      <c r="C1122" t="n">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr"/>
+      <c r="C1123" t="n">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr"/>
+      <c r="C1124" t="n">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr"/>
+      <c r="C1125" t="n">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr"/>
+      <c r="C1126" t="n">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr"/>
+      <c r="C1127" t="n">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr"/>
+      <c r="C1128" t="n">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr"/>
+      <c r="C1129" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr"/>
+      <c r="C1130" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr"/>
+      <c r="C1131" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr"/>
+      <c r="C1132" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr"/>
+      <c r="C1133" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr"/>
+      <c r="C1134" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr"/>
+      <c r="C1135" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr"/>
+      <c r="C1136" t="n">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr"/>
+      <c r="C1137" t="n">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr"/>
+      <c r="C1138" t="n">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr"/>
+      <c r="C1139" t="n">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr"/>
+      <c r="C1140" t="n">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr"/>
+      <c r="C1141" t="n">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr"/>
+      <c r="C1142" t="n">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr"/>
+      <c r="C1143" t="n">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr"/>
+      <c r="C1144" t="n">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr"/>
+      <c r="C1145" t="n">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1146" t="inlineStr"/>
+      <c r="C1146" t="n">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr"/>
+      <c r="C1147" t="n">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1148" t="inlineStr"/>
+      <c r="C1148" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1149" t="inlineStr"/>
+      <c r="C1149" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1150" t="inlineStr"/>
+      <c r="C1150" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1151" t="inlineStr"/>
+      <c r="C1151" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1152" t="inlineStr"/>
+      <c r="C1152" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr"/>
+      <c r="C1153" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr"/>
+      <c r="C1154" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr"/>
+      <c r="C1155" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1156" t="inlineStr"/>
+      <c r="C1156" t="n">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1157" t="inlineStr"/>
+      <c r="C1157" t="n">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr"/>
+      <c r="C1158" t="n">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr"/>
+      <c r="C1159" t="n">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr"/>
+      <c r="C1160" t="n">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1161" t="inlineStr"/>
+      <c r="C1161" t="n">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1162" t="inlineStr"/>
+      <c r="C1162" t="n">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1163" t="inlineStr"/>
+      <c r="C1163" t="n">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1164" t="inlineStr"/>
+      <c r="C1164" t="n">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1165" t="inlineStr"/>
+      <c r="C1165" t="n">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1166" t="inlineStr"/>
+      <c r="C1166" t="n">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1167" t="inlineStr"/>
+      <c r="C1167" t="n">
+        <v>259</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
